--- a/tests/testdata/testdata_multiple_sheets.xlsx
+++ b/tests/testdata/testdata_multiple_sheets.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-22.04\home\jef\repositories\gitea\foz\mango-metadata-from-tables\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\mariana\repos\gitea\foz\mango-metadata-from-tables\tests\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C85AB72C-F4E2-4B50-A6DC-4BDFDC8B8DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A6C46D-DFB8-4049-98E9-205F062B26D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -40,15 +40,6 @@
     <t>shape</t>
   </si>
   <si>
-    <t>/icts/home/datateam_icts_icts_test/mango-metadata-from-tables/file1.txt</t>
-  </si>
-  <si>
-    <t>/icts/home/datateam_icts_icts_test/mango-metadata-from-tables/file2.txt</t>
-  </si>
-  <si>
-    <t>/icts/home/datateam_icts_icts_test/mango-metadata-from-tables/file3.txt</t>
-  </si>
-  <si>
     <t>small</t>
   </si>
   <si>
@@ -80,6 +71,15 @@
   </si>
   <si>
     <t>like a forest on a sunny day</t>
+  </si>
+  <si>
+    <t>/icts/home/datateam_icts_icts_quality/mango-metadata-from-tables/file3.txt</t>
+  </si>
+  <si>
+    <t>/icts/home/datateam_icts_icts_quality/mango-metadata-from-tables/file1.txt</t>
+  </si>
+  <si>
+    <t>/icts/home/datateam_icts_icts_quality/mango-metadata-from-tables/file2.txt</t>
   </si>
 </sst>
 </file>
@@ -419,30 +419,30 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -472,24 +472,24 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
